--- a/2022 data/excel_outputs/141_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/141_boothwise_data.xlsx
@@ -14,11 +14,77 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="431">
   <si>
     <t>AC 141 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -1036,7 +1102,7 @@
     <t>PS SEMARIYA H/O CHAHLAR ROOM NO.1</t>
   </si>
   <si>
-    <t>####0##0 ####### #0 ##### #### ### 2</t>
+    <t>PS SEMARIYA H/O CHAHLAR ROOM ROOM NO. 338</t>
   </si>
   <si>
     <t>COMPOSITE SCHOOL RUDRAPUR (1 TO 8) ROOM NO.1</t>
@@ -1247,8 +1313,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1264,7 +1338,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1272,12 +1346,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1576,79 +1668,145 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:23">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>389</v>
+        <v>411</v>
       </c>
       <c r="D2" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="E2" t="s">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="F2" t="s">
-        <v>392</v>
+        <v>414</v>
       </c>
       <c r="G2" t="s">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="H2" t="s">
-        <v>394</v>
+        <v>416</v>
       </c>
       <c r="I2" t="s">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="J2" t="s">
-        <v>396</v>
+        <v>418</v>
       </c>
       <c r="K2" t="s">
-        <v>397</v>
+        <v>419</v>
       </c>
       <c r="L2" t="s">
-        <v>398</v>
+        <v>420</v>
       </c>
       <c r="M2" t="s">
-        <v>399</v>
+        <v>421</v>
       </c>
       <c r="N2" t="s">
-        <v>400</v>
+        <v>422</v>
       </c>
       <c r="O2" t="s">
-        <v>401</v>
+        <v>423</v>
       </c>
       <c r="P2" t="s">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="Q2" t="s">
-        <v>403</v>
+        <v>425</v>
       </c>
       <c r="R2" t="s">
-        <v>404</v>
+        <v>426</v>
       </c>
       <c r="S2" t="s">
-        <v>405</v>
+        <v>427</v>
       </c>
       <c r="T2" t="s">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="U2" t="s">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="V2" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="W2" t="s">
-        <v>408</v>
+        <v>430</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -1656,7 +1814,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C3">
         <v>1012</v>
@@ -1727,7 +1885,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>1007</v>
@@ -1798,7 +1956,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>912</v>
@@ -1869,7 +2027,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>1140</v>
@@ -1940,7 +2098,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>719</v>
@@ -2011,7 +2169,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>723</v>
@@ -2082,7 +2240,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C9">
         <v>1024</v>
@@ -2153,7 +2311,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>1147</v>
@@ -2224,7 +2382,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C11">
         <v>1127</v>
@@ -2295,7 +2453,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C12">
         <v>1045</v>
@@ -2366,7 +2524,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C13">
         <v>1007</v>
@@ -2437,7 +2595,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C14">
         <v>896</v>
@@ -2508,7 +2666,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C15">
         <v>840</v>
@@ -2579,7 +2737,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C16">
         <v>1142</v>
@@ -2650,7 +2808,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="C17">
         <v>1007</v>
@@ -2721,7 +2879,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C18">
         <v>822</v>
@@ -2792,7 +2950,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="C19">
         <v>693</v>
@@ -2863,7 +3021,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C20">
         <v>756</v>
@@ -2934,7 +3092,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C21">
         <v>1113</v>
@@ -3005,7 +3163,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C22">
         <v>1069</v>
@@ -3076,7 +3234,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C23">
         <v>1019</v>
@@ -3147,7 +3305,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C24">
         <v>1141</v>
@@ -3218,7 +3376,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C25">
         <v>1027</v>
@@ -3289,7 +3447,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="C26">
         <v>822</v>
@@ -3360,7 +3518,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="C27">
         <v>872</v>
@@ -3431,7 +3589,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C28">
         <v>985</v>
@@ -3502,7 +3660,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="C29">
         <v>821</v>
@@ -3573,7 +3731,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="C30">
         <v>1175</v>
@@ -3644,7 +3802,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C31">
         <v>1145</v>
@@ -3715,7 +3873,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C32">
         <v>1150</v>
@@ -3786,7 +3944,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C33">
         <v>1035</v>
@@ -3857,7 +4015,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C34">
         <v>1180</v>
@@ -3928,7 +4086,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C35">
         <v>1192</v>
@@ -3999,7 +4157,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="C36">
         <v>731</v>
@@ -4070,7 +4228,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C37">
         <v>710</v>
@@ -4141,7 +4299,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="C38">
         <v>681</v>
@@ -4212,7 +4370,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="C39">
         <v>535</v>
@@ -4283,7 +4441,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="C40">
         <v>998</v>
@@ -4354,7 +4512,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="C41">
         <v>914</v>
@@ -4425,7 +4583,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="C42">
         <v>965</v>
@@ -4496,7 +4654,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C43">
         <v>1156</v>
@@ -4567,7 +4725,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="C44">
         <v>1067</v>
@@ -4638,7 +4796,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="C45">
         <v>948</v>
@@ -4709,7 +4867,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C46">
         <v>895</v>
@@ -4780,7 +4938,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="C47">
         <v>1056</v>
@@ -4851,7 +5009,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="C48">
         <v>760</v>
@@ -4922,7 +5080,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="C49">
         <v>877</v>
@@ -4993,7 +5151,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C50">
         <v>786</v>
@@ -5064,7 +5222,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="C51">
         <v>1103</v>
@@ -5135,7 +5293,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="C52">
         <v>1076</v>
@@ -5206,7 +5364,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C53">
         <v>1052</v>
@@ -5277,7 +5435,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="C54">
         <v>993</v>
@@ -5348,7 +5506,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="C55">
         <v>870</v>
@@ -5419,7 +5577,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C56">
         <v>998</v>
@@ -5490,7 +5648,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C57">
         <v>654</v>
@@ -5561,7 +5719,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C58">
         <v>1067</v>
@@ -5632,7 +5790,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C59">
         <v>831</v>
@@ -5703,7 +5861,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="C60">
         <v>744</v>
@@ -5774,7 +5932,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C61">
         <v>1190</v>
@@ -5845,7 +6003,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="C62">
         <v>1234</v>
@@ -5916,7 +6074,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="C63">
         <v>1224</v>
@@ -5987,7 +6145,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="C64">
         <v>1110</v>
@@ -6058,7 +6216,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="C65">
         <v>752</v>
@@ -6129,7 +6287,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="C66">
         <v>853</v>
@@ -6200,7 +6358,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="C67">
         <v>703</v>
@@ -6271,7 +6429,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="C68">
         <v>704</v>
@@ -6342,7 +6500,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="C69">
         <v>694</v>
@@ -6413,7 +6571,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="C70">
         <v>745</v>
@@ -6484,7 +6642,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="C71">
         <v>827</v>
@@ -6555,7 +6713,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="C72">
         <v>945</v>
@@ -6626,7 +6784,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="C73">
         <v>802</v>
@@ -6697,7 +6855,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="C74">
         <v>1073</v>
@@ -6768,7 +6926,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C75">
         <v>857</v>
@@ -6839,7 +6997,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="C76">
         <v>738</v>
@@ -6910,7 +7068,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="C77">
         <v>907</v>
@@ -6981,7 +7139,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="C78">
         <v>741</v>
@@ -7052,7 +7210,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="C79">
         <v>986</v>
@@ -7123,7 +7281,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="C80">
         <v>912</v>
@@ -7194,7 +7352,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C81">
         <v>653</v>
@@ -7265,7 +7423,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="C82">
         <v>637</v>
@@ -7336,7 +7494,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="C83">
         <v>1053</v>
@@ -7407,7 +7565,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="C84">
         <v>821</v>
@@ -7478,7 +7636,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="C85">
         <v>933</v>
@@ -7549,7 +7707,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="C86">
         <v>958</v>
@@ -7620,7 +7778,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="C87">
         <v>1078</v>
@@ -7691,7 +7849,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="C88">
         <v>856</v>
@@ -7762,7 +7920,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="C89">
         <v>650</v>
@@ -7833,7 +7991,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="C90">
         <v>572</v>
@@ -7904,7 +8062,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="C91">
         <v>1041</v>
@@ -7975,7 +8133,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C92">
         <v>533</v>
@@ -8046,7 +8204,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="C93">
         <v>649</v>
@@ -8117,7 +8275,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="C94">
         <v>505</v>
@@ -8188,7 +8346,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="C95">
         <v>848</v>
@@ -8259,7 +8417,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="C96">
         <v>722</v>
@@ -8330,7 +8488,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="C97">
         <v>697</v>
@@ -8401,7 +8559,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="C98">
         <v>913</v>
@@ -8472,7 +8630,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="C99">
         <v>827</v>
@@ -8543,7 +8701,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="C100">
         <v>896</v>
@@ -8614,7 +8772,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="C101">
         <v>680</v>
@@ -8685,7 +8843,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="C102">
         <v>660</v>
@@ -8756,7 +8914,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="C103">
         <v>681</v>
@@ -8827,7 +8985,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="C104">
         <v>719</v>
@@ -8898,7 +9056,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="C105">
         <v>798</v>
@@ -8969,7 +9127,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="C106">
         <v>595</v>
@@ -9040,7 +9198,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="C107">
         <v>698</v>
@@ -9111,7 +9269,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="C108">
         <v>1007</v>
@@ -9182,7 +9340,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="C109">
         <v>709</v>
@@ -9253,7 +9411,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="C110">
         <v>615</v>
@@ -9324,7 +9482,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="C111">
         <v>610</v>
@@ -9395,7 +9553,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="C112">
         <v>1025</v>
@@ -9466,7 +9624,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="C113">
         <v>974</v>
@@ -9537,7 +9695,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="C114">
         <v>1057</v>
@@ -9608,7 +9766,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="C115">
         <v>916</v>
@@ -9679,7 +9837,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="C116">
         <v>1007</v>
@@ -9750,7 +9908,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="C117">
         <v>736</v>
@@ -9821,7 +9979,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="C118">
         <v>1125</v>
@@ -9892,7 +10050,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="C119">
         <v>1009</v>
@@ -9963,7 +10121,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="C120">
         <v>1077</v>
@@ -10034,7 +10192,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="C121">
         <v>932</v>
@@ -10105,7 +10263,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="C122">
         <v>1075</v>
@@ -10176,7 +10334,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="C123">
         <v>918</v>
@@ -10247,7 +10405,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="C124">
         <v>917</v>
@@ -10318,7 +10476,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="C125">
         <v>1085</v>
@@ -10389,7 +10547,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="C126">
         <v>854</v>
@@ -10460,7 +10618,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="C127">
         <v>932</v>
@@ -10531,7 +10689,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="C128">
         <v>1070</v>
@@ -10602,7 +10760,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="C129">
         <v>1136</v>
@@ -10673,7 +10831,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="C130">
         <v>1140</v>
@@ -10744,7 +10902,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="C131">
         <v>1085</v>
@@ -10815,7 +10973,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="C132">
         <v>1123</v>
@@ -10886,7 +11044,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="C133">
         <v>739</v>
@@ -10957,7 +11115,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="C134">
         <v>603</v>
@@ -11028,7 +11186,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="C135">
         <v>719</v>
@@ -11099,7 +11257,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="C136">
         <v>700</v>
@@ -11170,7 +11328,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="C137">
         <v>685</v>
@@ -11241,7 +11399,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="C138">
         <v>776</v>
@@ -11312,7 +11470,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="C139">
         <v>638</v>
@@ -11383,7 +11541,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="C140">
         <v>810</v>
@@ -11454,7 +11612,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="C141">
         <v>893</v>
@@ -11525,7 +11683,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="C142">
         <v>866</v>
@@ -11596,7 +11754,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="C143">
         <v>994</v>
@@ -11667,7 +11825,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="C144">
         <v>698</v>
@@ -11738,7 +11896,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="C145">
         <v>610</v>
@@ -11809,7 +11967,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="C146">
         <v>1122</v>
@@ -11880,7 +12038,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="C147">
         <v>1063</v>
@@ -11951,7 +12109,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="C148">
         <v>1090</v>
@@ -12022,7 +12180,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="C149">
         <v>1111</v>
@@ -12093,7 +12251,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="C150">
         <v>976</v>
@@ -12164,7 +12322,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="C151">
         <v>1019</v>
@@ -12235,7 +12393,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="C152">
         <v>1074</v>
@@ -12306,7 +12464,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="C153">
         <v>629</v>
@@ -12377,7 +12535,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="C154">
         <v>673</v>
@@ -12448,7 +12606,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="C155">
         <v>660</v>
@@ -12519,7 +12677,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="C156">
         <v>1117</v>
@@ -12590,7 +12748,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="C157">
         <v>973</v>
@@ -12661,7 +12819,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="C158">
         <v>1077</v>
@@ -12732,7 +12890,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="C159">
         <v>1009</v>
@@ -12803,7 +12961,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="C160">
         <v>700</v>
@@ -12874,7 +13032,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="C161">
         <v>827</v>
@@ -12945,7 +13103,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="C162">
         <v>615</v>
@@ -13016,7 +13174,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="C163">
         <v>1166</v>
@@ -13087,7 +13245,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="C164">
         <v>1069</v>
@@ -13158,7 +13316,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="C165">
         <v>816</v>
@@ -13229,7 +13387,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="C166">
         <v>920</v>
@@ -13300,7 +13458,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="C167">
         <v>875</v>
@@ -13371,7 +13529,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="C168">
         <v>823</v>
@@ -13442,7 +13600,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="C169">
         <v>787</v>
@@ -13513,7 +13671,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="C170">
         <v>703</v>
@@ -13584,7 +13742,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="C171">
         <v>779</v>
@@ -13655,7 +13813,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="C172">
         <v>696</v>
@@ -13726,7 +13884,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="C173">
         <v>639</v>
@@ -13797,7 +13955,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="C174">
         <v>1033</v>
@@ -13868,7 +14026,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="C175">
         <v>1004</v>
@@ -13939,7 +14097,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="C176">
         <v>1031</v>
@@ -14010,7 +14168,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="C177">
         <v>973</v>
@@ -14081,7 +14239,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="C178">
         <v>596</v>
@@ -14152,7 +14310,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="C179">
         <v>719</v>
@@ -14223,7 +14381,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="C180">
         <v>582</v>
@@ -14294,7 +14452,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="C181">
         <v>626</v>
@@ -14365,7 +14523,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="C182">
         <v>1091</v>
@@ -14436,7 +14594,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="C183">
         <v>1101</v>
@@ -14507,7 +14665,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="C184">
         <v>1121</v>
@@ -14578,7 +14736,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="C185">
         <v>819</v>
@@ -14649,7 +14807,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="C186">
         <v>975</v>
@@ -14720,7 +14878,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="C187">
         <v>897</v>
@@ -14791,7 +14949,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="C188">
         <v>587</v>
@@ -14862,7 +15020,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="C189">
         <v>592</v>
@@ -14933,7 +15091,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="C190">
         <v>1004</v>
@@ -15004,7 +15162,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="C191">
         <v>769</v>
@@ -15075,7 +15233,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="C192">
         <v>674</v>
@@ -15146,7 +15304,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="C193">
         <v>577</v>
@@ -15217,7 +15375,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="C194">
         <v>901</v>
@@ -15288,7 +15446,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="C195">
         <v>956</v>
@@ -15359,7 +15517,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="C196">
         <v>919</v>
@@ -15430,7 +15588,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="C197">
         <v>1055</v>
@@ -15501,7 +15659,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="C198">
         <v>1057</v>
@@ -15572,7 +15730,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="C199">
         <v>759</v>
@@ -15643,7 +15801,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="C200">
         <v>754</v>
@@ -15714,7 +15872,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="C201">
         <v>1113</v>
@@ -15785,7 +15943,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="C202">
         <v>962</v>
@@ -15856,7 +16014,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="C203">
         <v>770</v>
@@ -15927,7 +16085,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="C204">
         <v>806</v>
@@ -15998,7 +16156,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="C205">
         <v>976</v>
@@ -16069,7 +16227,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="C206">
         <v>951</v>
@@ -16140,7 +16298,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="C207">
         <v>641</v>
@@ -16211,7 +16369,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="C208">
         <v>584</v>
@@ -16282,7 +16440,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="C209">
         <v>1116</v>
@@ -16353,7 +16511,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="C210">
         <v>1162</v>
@@ -16424,7 +16582,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="C211">
         <v>684</v>
@@ -16495,7 +16653,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="C212">
         <v>668</v>
@@ -16566,7 +16724,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="C213">
         <v>512</v>
@@ -16637,7 +16795,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="C214">
         <v>865</v>
@@ -16708,7 +16866,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="C215">
         <v>790</v>
@@ -16779,7 +16937,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="C216">
         <v>1086</v>
@@ -16850,7 +17008,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="C217">
         <v>1000</v>
@@ -16921,7 +17079,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="C218">
         <v>1171</v>
@@ -16992,7 +17150,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="C219">
         <v>839</v>
@@ -17063,7 +17221,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="C220">
         <v>867</v>
@@ -17134,7 +17292,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="C221">
         <v>921</v>
@@ -17205,7 +17363,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="C222">
         <v>674</v>
@@ -17276,7 +17434,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="C223">
         <v>844</v>
@@ -17347,7 +17505,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="C224">
         <v>1103</v>
@@ -17418,7 +17576,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="C225">
         <v>800</v>
@@ -17489,7 +17647,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="C226">
         <v>785</v>
@@ -17560,7 +17718,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="C227">
         <v>729</v>
@@ -17631,7 +17789,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="C228">
         <v>684</v>
@@ -17702,7 +17860,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="C229">
         <v>1080</v>
@@ -17773,7 +17931,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="C230">
         <v>801</v>
@@ -17844,7 +18002,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="C231">
         <v>971</v>
@@ -17915,7 +18073,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="C232">
         <v>618</v>
@@ -17986,7 +18144,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="C233">
         <v>590</v>
@@ -18057,7 +18215,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="C234">
         <v>445</v>
@@ -18128,7 +18286,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="C235">
         <v>983</v>
@@ -18199,7 +18357,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="C236">
         <v>1002</v>
@@ -18270,7 +18428,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="C237">
         <v>1063</v>
@@ -18341,7 +18499,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="C238">
         <v>1004</v>
@@ -18412,7 +18570,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="C239">
         <v>763</v>
@@ -18483,7 +18641,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="C240">
         <v>793</v>
@@ -18554,7 +18712,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="C241">
         <v>587</v>
@@ -18625,7 +18783,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="C242">
         <v>711</v>
@@ -18696,7 +18854,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="C243">
         <v>699</v>
@@ -18767,7 +18925,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="C244">
         <v>710</v>
@@ -18838,7 +18996,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="C245">
         <v>720</v>
@@ -18909,7 +19067,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="C246">
         <v>827</v>
@@ -18980,7 +19138,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="C247">
         <v>891</v>
@@ -19051,7 +19209,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="C248">
         <v>879</v>
@@ -19122,7 +19280,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="C249">
         <v>601</v>
@@ -19193,7 +19351,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="C250">
         <v>662</v>
@@ -19264,7 +19422,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="C251">
         <v>706</v>
@@ -19335,7 +19493,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="C252">
         <v>495</v>
@@ -19406,7 +19564,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="C253">
         <v>550</v>
@@ -19477,7 +19635,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="C254">
         <v>608</v>
@@ -19548,7 +19706,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="C255">
         <v>695</v>
@@ -19619,7 +19777,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="C256">
         <v>709</v>
@@ -19690,7 +19848,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="C257">
         <v>1161</v>
@@ -19761,7 +19919,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="C258">
         <v>1025</v>
@@ -19832,7 +19990,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="C259">
         <v>1015</v>
@@ -19903,7 +20061,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="C260">
         <v>1066</v>
@@ -19974,7 +20132,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="C261">
         <v>930</v>
@@ -20045,7 +20203,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="C262">
         <v>304</v>
@@ -20116,7 +20274,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="C263">
         <v>750</v>
@@ -20187,7 +20345,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="C264">
         <v>996</v>
@@ -20258,7 +20416,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="C265">
         <v>855</v>
@@ -20329,7 +20487,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="C266">
         <v>886</v>
@@ -20400,7 +20558,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="C267">
         <v>602</v>
@@ -20471,7 +20629,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="C268">
         <v>885</v>
@@ -20542,7 +20700,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="C269">
         <v>869</v>
@@ -20613,7 +20771,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="C270">
         <v>914</v>
@@ -20684,7 +20842,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="C271">
         <v>1072</v>
@@ -20755,7 +20913,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="C272">
         <v>911</v>
@@ -20826,7 +20984,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="C273">
         <v>922</v>
@@ -20897,7 +21055,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="C274">
         <v>634</v>
@@ -20968,7 +21126,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="C275">
         <v>667</v>
@@ -21039,7 +21197,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="C276">
         <v>567</v>
@@ -21110,7 +21268,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="C277">
         <v>721</v>
@@ -21181,7 +21339,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="C278">
         <v>675</v>
@@ -21252,7 +21410,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="C279">
         <v>877</v>
@@ -21323,7 +21481,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="C280">
         <v>1125</v>
@@ -21394,7 +21552,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="C281">
         <v>1023</v>
@@ -21465,7 +21623,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="C282">
         <v>960</v>
@@ -21536,7 +21694,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="C283">
         <v>1079</v>
@@ -21607,7 +21765,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="C284">
         <v>1040</v>
@@ -21678,7 +21836,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="C285">
         <v>1036</v>
@@ -21749,7 +21907,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="C286">
         <v>1042</v>
@@ -21820,7 +21978,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>287</v>
+        <v>309</v>
       </c>
       <c r="C287">
         <v>660</v>
@@ -21891,7 +22049,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="C288">
         <v>744</v>
@@ -21962,7 +22120,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="C289">
         <v>711</v>
@@ -22033,7 +22191,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="C290">
         <v>516</v>
@@ -22104,7 +22262,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="C291">
         <v>1021</v>
@@ -22175,7 +22333,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="C292">
         <v>856</v>
@@ -22246,7 +22404,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>293</v>
+        <v>315</v>
       </c>
       <c r="C293">
         <v>830</v>
@@ -22317,7 +22475,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="C294">
         <v>703</v>
@@ -22388,7 +22546,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="C295">
         <v>1147</v>
@@ -22459,7 +22617,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="C296">
         <v>603</v>
@@ -22530,7 +22688,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="C297">
         <v>581</v>
@@ -22601,7 +22759,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="C298">
         <v>866</v>
@@ -22672,7 +22830,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="C299">
         <v>669</v>
@@ -22743,7 +22901,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="C300">
         <v>677</v>
@@ -22814,7 +22972,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="C301">
         <v>640</v>
@@ -22885,7 +23043,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="C302">
         <v>696</v>
@@ -22956,7 +23114,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="C303">
         <v>600</v>
@@ -23027,7 +23185,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C304">
         <v>876</v>
@@ -23098,7 +23256,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="C305">
         <v>733</v>
@@ -23169,7 +23327,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="C306">
         <v>564</v>
@@ -23240,7 +23398,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="C307">
         <v>658</v>
@@ -23311,7 +23469,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="C308">
         <v>459</v>
@@ -23382,7 +23540,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="C309">
         <v>670</v>
@@ -23453,7 +23611,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="C310">
         <v>612</v>
@@ -23524,7 +23682,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="C311">
         <v>728</v>
@@ -23595,7 +23753,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="C312">
         <v>613</v>
@@ -23666,7 +23824,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="C313">
         <v>723</v>
@@ -23737,7 +23895,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>314</v>
+        <v>336</v>
       </c>
       <c r="C314">
         <v>740</v>
@@ -23808,7 +23966,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="C315">
         <v>940</v>
@@ -23879,7 +24037,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="C316">
         <v>973</v>
@@ -23950,7 +24108,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="C317">
         <v>1162</v>
@@ -24021,7 +24179,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="C318">
         <v>778</v>
@@ -24092,7 +24250,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="C319">
         <v>663</v>
@@ -24163,7 +24321,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="C320">
         <v>681</v>
@@ -24234,7 +24392,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="C321">
         <v>624</v>
@@ -24305,7 +24463,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="C322">
         <v>563</v>
@@ -24376,7 +24534,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="C323">
         <v>953</v>
@@ -24447,7 +24605,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="C324">
         <v>612</v>
@@ -24518,7 +24676,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="C325">
         <v>617</v>
@@ -24589,7 +24747,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="C326">
         <v>829</v>
@@ -24660,7 +24818,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="C327">
         <v>1083</v>
@@ -24731,7 +24889,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="C328">
         <v>808</v>
@@ -24802,7 +24960,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="C329">
         <v>519</v>
@@ -24873,7 +25031,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="C330">
         <v>911</v>
@@ -24944,7 +25102,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="C331">
         <v>891</v>
@@ -25015,7 +25173,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="C332">
         <v>1056</v>
@@ -25086,7 +25244,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="C333">
         <v>694</v>
@@ -25157,7 +25315,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="C334">
         <v>1046</v>
@@ -25228,7 +25386,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="C335">
         <v>1075</v>
@@ -25299,7 +25457,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="C336">
         <v>1146</v>
@@ -25370,7 +25528,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="C337">
         <v>1142</v>
@@ -25441,7 +25599,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="C338">
         <v>1154</v>
@@ -25512,7 +25670,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="C339">
         <v>706</v>
@@ -25583,7 +25741,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="C340">
         <v>703</v>
@@ -25654,7 +25812,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="C341">
         <v>1064</v>
@@ -25725,7 +25883,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="C342">
         <v>829</v>
@@ -25796,7 +25954,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="C343">
         <v>999</v>
@@ -25867,7 +26025,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="C344">
         <v>1168</v>
@@ -25938,7 +26096,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="C345">
         <v>800</v>
@@ -26009,7 +26167,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="C346">
         <v>1135</v>
@@ -26080,7 +26238,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="C347">
         <v>657</v>
@@ -26151,7 +26309,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="C348">
         <v>675</v>
@@ -26222,7 +26380,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="C349">
         <v>1037</v>
@@ -26293,7 +26451,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="C350">
         <v>1055</v>
@@ -26364,7 +26522,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="C351">
         <v>993</v>
@@ -26435,7 +26593,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="C352">
         <v>848</v>
@@ -26506,7 +26664,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="C353">
         <v>970</v>
@@ -26577,7 +26735,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="C354">
         <v>727</v>
@@ -26648,7 +26806,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="C355">
         <v>690</v>
@@ -26719,7 +26877,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="C356">
         <v>730</v>
@@ -26790,7 +26948,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="C357">
         <v>774</v>
@@ -26861,7 +27019,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="C358">
         <v>828</v>
@@ -26932,7 +27090,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="C359">
         <v>600</v>
@@ -27003,7 +27161,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="C360">
         <v>1118</v>
@@ -27074,7 +27232,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="C361">
         <v>959</v>
@@ -27145,7 +27303,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="C362">
         <v>1085</v>
@@ -27216,7 +27374,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>363</v>
+        <v>385</v>
       </c>
       <c r="C363">
         <v>1106</v>
@@ -27287,7 +27445,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="C364">
         <v>1144</v>
@@ -27358,7 +27516,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="C365">
         <v>1196</v>
@@ -27429,7 +27587,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>366</v>
+        <v>388</v>
       </c>
       <c r="C366">
         <v>1161</v>
@@ -27500,7 +27658,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="C367">
         <v>665</v>
@@ -27571,7 +27729,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>368</v>
+        <v>390</v>
       </c>
       <c r="C368">
         <v>533</v>
@@ -27642,7 +27800,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>369</v>
+        <v>391</v>
       </c>
       <c r="C369">
         <v>1002</v>
@@ -27713,7 +27871,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>370</v>
+        <v>392</v>
       </c>
       <c r="C370">
         <v>650</v>
@@ -27784,7 +27942,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>371</v>
+        <v>393</v>
       </c>
       <c r="C371">
         <v>527</v>
@@ -27855,7 +28013,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>372</v>
+        <v>394</v>
       </c>
       <c r="C372">
         <v>653</v>
@@ -27926,7 +28084,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>373</v>
+        <v>395</v>
       </c>
       <c r="C373">
         <v>694</v>
@@ -27997,7 +28155,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>374</v>
+        <v>396</v>
       </c>
       <c r="C374">
         <v>785</v>
@@ -28068,7 +28226,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>375</v>
+        <v>397</v>
       </c>
       <c r="C375">
         <v>920</v>
@@ -28139,7 +28297,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>376</v>
+        <v>398</v>
       </c>
       <c r="C376">
         <v>973</v>
@@ -28210,7 +28368,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>377</v>
+        <v>399</v>
       </c>
       <c r="C377">
         <v>878</v>
@@ -28281,7 +28439,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="C378">
         <v>717</v>
@@ -28352,7 +28510,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>379</v>
+        <v>401</v>
       </c>
       <c r="C379">
         <v>1090</v>
@@ -28423,7 +28581,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>380</v>
+        <v>402</v>
       </c>
       <c r="C380">
         <v>1160</v>
@@ -28494,7 +28652,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="C381">
         <v>1029</v>
@@ -28565,7 +28723,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="C382">
         <v>872</v>
@@ -28636,7 +28794,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>383</v>
+        <v>405</v>
       </c>
       <c r="C383">
         <v>764</v>
@@ -28707,7 +28865,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>384</v>
+        <v>406</v>
       </c>
       <c r="C384">
         <v>705</v>
@@ -28778,7 +28936,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>385</v>
+        <v>407</v>
       </c>
       <c r="C385">
         <v>947</v>
@@ -28849,7 +29007,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>386</v>
+        <v>408</v>
       </c>
       <c r="C386">
         <v>682</v>
@@ -28920,7 +29078,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>387</v>
+        <v>409</v>
       </c>
       <c r="C387">
         <v>753</v>
@@ -28991,7 +29149,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>388</v>
+        <v>410</v>
       </c>
       <c r="C388">
         <v>706</v>
